--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,12 +495,45 @@
       <c r="F2" t="n">
         <v>35</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>1520714</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensores de Cambaceres vs Berazategui</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Primera C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1499945</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,111 @@
       <c r="F3" t="n">
         <v>36.1</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>1499945</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Midland vs Atlanta</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F4" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1498607</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Villa San Carlos vs UAI Urquiza</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1499473</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Colegiales vs San Martin Tucuman</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1498601</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,12 +627,45 @@
       <c r="F6" t="n">
         <v>37</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>1498601</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Argentino Quilmes vs Deportivo Armenio</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1499463</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,12 +660,144 @@
       <c r="F7" t="n">
         <v>36.4</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>1499463</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Deportivo Laferrere vs Defensores Unidos</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F8" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1499480</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UAI Urquiza vs San Martín Burzaco</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F9" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1499483</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Almagro vs Atlanta</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1498344</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Colegiales vs Quilmes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="F11" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1498351</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,12 +792,78 @@
       <c r="F11" t="n">
         <v>36.5</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>1498351</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Santamarina vs Villa Mitre</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Torneo Federal A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="F12" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1530416</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Monte Roraima vs Guaporé</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Serie D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F13" t="n">
+        <v>36</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1554043</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -858,12 +858,144 @@
       <c r="F13" t="n">
         <v>36</v>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>1554043</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Argentino de Merlo vs Dock Sud</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="F14" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1499474</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Talleres Remedios vs Comunicaciones</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F15" t="n">
+        <v>34</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1499482</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn vs Los Andes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>37</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1498353</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Juventus SC vs Tubarao</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Catarinense - 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F17" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1541986</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,12 +990,45 @@
       <c r="F17" t="n">
         <v>33.6</v>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>1541986</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>America Mineiro vs Criciuma</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Serie B</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="F18" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1520730</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -1023,9 +1023,21 @@
       <c r="F18" t="n">
         <v>34.2</v>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NO empate</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>1520730</t>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,6 +1044,42 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brown DE Adrogue vs Flandria</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F19" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1499487</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,12 +1071,45 @@
       <c r="F19" t="n">
         <v>36.1</v>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>1499487</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tombense vs CRAC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Serie D</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="F20" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1554061</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -1104,9 +1104,21 @@
       <c r="F20" t="n">
         <v>33.4</v>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>1554061</t>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1125,6 +1125,108 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Deportivo Laferrere vs Argentino Quilmes</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F21" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1499490</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Liniers vs Villa San Carlos</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="F22" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1499491</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sportivo Barracas vs Lujan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Primera C</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F23" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1499965</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,12 +1218,111 @@
       <c r="F23" t="n">
         <v>36.2</v>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>1499965</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>9 de Julio Rafaela vs Gimnasia Chivilcoy</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Torneo Federal A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="F24" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1530418</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sarmiento de La Banda vs Bartolomé Mitre</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Torneo Federal A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F25" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1530430</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sarmiento Resistencia vs Tucuman Central</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Torneo Federal A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F26" t="n">
+        <v>35</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1530431</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1317,12 +1317,78 @@
       <c r="F26" t="n">
         <v>35</v>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>1530431</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Central Ballester vs Atletico Atlas</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Primera C</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F27" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1499954</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Claypole vs Canuelas</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Primera C</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1499956</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1383,12 +1383,78 @@
       <c r="F28" t="n">
         <v>33.9</v>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>1499956</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pocheon vs Daejeon Korail</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FA Cup</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F29" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1557957</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ulsan Citizen vs Chuncheon</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FA Cup</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F30" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1557961</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1449,12 +1449,111 @@
       <c r="F30" t="n">
         <v>33.6</v>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>1557961</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deportivo Camioneros vs UAI Urquiza</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F31" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1499501</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Lugano vs JJ Urquiza</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Primera C</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F32" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1499976</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ituzaingó vs Villa San Carlos</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F33" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1499504</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1548,12 +1548,144 @@
       <c r="F33" t="n">
         <v>34.7</v>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>1499504</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quilmes vs Atlanta</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F34" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1498628</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Goiatuba EC vs Manauara</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Serie D</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="F35" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1567799</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Confiança vs Barra</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Serie C</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F36" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1526878</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Velo Clube vs São Luiz</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Serie D</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="F37" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1567808</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1647,6 +1647,21 @@
       <c r="F36" t="n">
         <v>33.6</v>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>NO empate</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>1526878</t>
@@ -1680,12 +1695,354 @@
       <c r="F37" t="n">
         <v>35.2</v>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>NO empate</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>1567808</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Argentino Quilmes vs Talleres Remedios</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F38" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1499496</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sportivo Italiano vs Real Pilar</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F39" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1499506</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sacachispas vs Juventud Unida</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Primera C</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F40" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1499977</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Victoriano Arenas vs Deportivo Paraguayo</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Primera C</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F41" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1499979</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Gramadense vs Bagé</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Copa Gaúcha</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="F42" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1557277</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Boca Juniors Res. vs River Plate Res.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Reserve League</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F43" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1567792</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CA Estudiantes vs Racing Cordoba</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F44" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1498615</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn vs Colon Santa Fe</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Primera Nacional</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F45" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1498622</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Canuelas vs Central Cordoba</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Primera C</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F46" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1499970</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Atenas vs Fundacion Amigos</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Torneo Federal A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F47" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1530436</t>
         </is>
       </c>
     </row>

--- a/registro_empates.xlsx
+++ b/registro_empates.xlsx
@@ -1743,6 +1743,21 @@
       <c r="F38" t="n">
         <v>36.6</v>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NO empate</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>1499496</t>
@@ -1776,6 +1791,21 @@
       <c r="F39" t="n">
         <v>36.4</v>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>1499506</t>
@@ -1809,6 +1839,21 @@
       <c r="F40" t="n">
         <v>35.1</v>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NO empate</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>1499977</t>
@@ -1842,6 +1887,21 @@
       <c r="F41" t="n">
         <v>34.1</v>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>1499979</t>
@@ -1875,6 +1935,21 @@
       <c r="F42" t="n">
         <v>34.2</v>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NO empate</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>1557277</t>
@@ -1907,6 +1982,21 @@
       </c>
       <c r="F43" t="n">
         <v>33.7</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
